--- a/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTechs_TRA_Transformation.xlsx
+++ b/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTechs_TRA_Transformation.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AFA</t>
+          <t>AFA~2024</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.0435745305541326</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0.1053051155058204</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.2142414418911519</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0.0528331340874502</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0.1276800740446714</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.2597629092632971</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.0482132143007036</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0.1165152678933672</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.2370483036451265</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.0435745305502261</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0.1053051154963799</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.2142414418719453</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.0426080764479303</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0.0983263302644546</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.1868200275024638</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0.0731629056589151</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0.1688374745974963</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0.3207912017352431</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0.0522962054991771</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0.1206835511519473</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0.2292987471886999</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0.003603234198537</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0.0136922899544407</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.0547691598177629</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>0.0036032342469761</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>0.0136922901385095</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0.0547691605540382</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>0.0944788998907402</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>0.2645409196940727</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>0.5857691793225895</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>0.1652872008547008</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>0.4628041623931623</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1.024780645299145</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>0.0253615173336338</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>0.086953773715316</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>0.2499920994315336</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>0.0253615173913043</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0.0869537739130434</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>0.2499921</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0.0481892526079986</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.1505914143999956</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.3975613340159885</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.0481892592592592</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0.1505914351851852</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.3975613888888888</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>0.2193740336462519</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0.5568725469481779</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>0.9281209115802966</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>0.1908553411607143</t>
+          <t>0.2175</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0.21279281263686434</t>
+          <t>0.2425</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>0.4844789429464287</t>
+          <t>0.5655</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>0.5401663705397325</t>
+          <t>0.6305</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>0.8074649049107145</t>
+          <t>0.957</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>0.9002772842328877</t>
+          <t>1.067</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>0.0528331340874502</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0.1276800740446714</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0.2597629092632971</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>0.0731629056589151</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>0.1688374745974963</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0.3207912017352431</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>0.0253615173336338</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0.086953773715316</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0.2499920994315336</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>0.0481892526079986</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>0.1505914143999956</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>0.3975613340159885</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>0.2193740336462519</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0.5568725469481779</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>0.9281209115802966</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0.0944788998907402</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>0.2645409196940727</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>0.5857691793225895</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0.04357453050826</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0.04357453050826</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0.1053051153949616</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0.1053051153949616</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0.2142414416656117</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>0.2142414416656117</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0.0528331340874502</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0.1276800740446714</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0.2597629092632971</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>0.0482132143007036</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0.1165152678933672</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>0.2370483036451265</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>0.0731629056589151</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0.1688374745974963</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0.3207912017352431</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.0522962054991771</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.1206835511519473</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.2292987471886999</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="G175" t="n">
